--- a/productos.xlsx
+++ b/productos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Windows 10\Desktop\Pagina distri\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1D6CE45-FF4E-4D2E-ABB3-BC6C50207551}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD6F16DC-3D08-442A-962C-6117BDF5AB5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="606" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7787" uniqueCount="4044">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7787" uniqueCount="4043">
   <si>
     <t>id</t>
   </si>
@@ -12078,9 +12078,6 @@
   </si>
   <si>
     <t xml:space="preserve">importado </t>
-  </si>
-  <si>
-    <t>Construccion</t>
   </si>
   <si>
     <t>Plomeria</t>
@@ -15570,7 +15567,7 @@
         <v>19</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>4017</v>
+        <v>31</v>
       </c>
       <c r="H58" s="2"/>
       <c r="I58" s="2"/>
@@ -15845,7 +15842,7 @@
         <v>19</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>4018</v>
+        <v>4017</v>
       </c>
       <c r="H69" s="2" t="s">
         <v>574</v>
@@ -16748,7 +16745,7 @@
         <v>19</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>4019</v>
+        <v>4018</v>
       </c>
       <c r="H105" s="2"/>
       <c r="I105" s="2"/>
@@ -17649,7 +17646,7 @@
         <v>19</v>
       </c>
       <c r="G141" s="2" t="s">
-        <v>4018</v>
+        <v>4017</v>
       </c>
       <c r="H141" s="2"/>
       <c r="I141" s="2"/>
@@ -19085,7 +19082,7 @@
         <v>19</v>
       </c>
       <c r="G199" s="2" t="s">
-        <v>4019</v>
+        <v>4018</v>
       </c>
       <c r="H199" s="2"/>
       <c r="I199" s="2"/>
@@ -19110,7 +19107,7 @@
         <v>19</v>
       </c>
       <c r="G200" s="2" t="s">
-        <v>4019</v>
+        <v>4018</v>
       </c>
       <c r="H200" s="2"/>
       <c r="I200" s="2"/>
@@ -19135,7 +19132,7 @@
         <v>19</v>
       </c>
       <c r="G201" s="2" t="s">
-        <v>4019</v>
+        <v>4018</v>
       </c>
       <c r="H201" s="2"/>
       <c r="I201" s="2"/>
@@ -19306,7 +19303,7 @@
         <v>19</v>
       </c>
       <c r="G208" s="2" t="s">
-        <v>4019</v>
+        <v>4018</v>
       </c>
       <c r="J208" s="3"/>
       <c r="K208" s="11"/>
@@ -19329,7 +19326,7 @@
         <v>19</v>
       </c>
       <c r="G209" s="2" t="s">
-        <v>4030</v>
+        <v>4029</v>
       </c>
       <c r="H209" s="2"/>
       <c r="I209" s="2"/>
@@ -19353,7 +19350,7 @@
         <v>19</v>
       </c>
       <c r="G210" s="2" t="s">
-        <v>4030</v>
+        <v>4029</v>
       </c>
       <c r="H210" s="2"/>
       <c r="I210" s="2"/>
@@ -19376,7 +19373,7 @@
       <c r="E211" s="190"/>
       <c r="F211" s="33"/>
       <c r="G211" s="2" t="s">
-        <v>4030</v>
+        <v>4029</v>
       </c>
       <c r="H211" s="2"/>
       <c r="I211" s="2"/>
@@ -19401,7 +19398,7 @@
         <v>19</v>
       </c>
       <c r="G212" s="2" t="s">
-        <v>4030</v>
+        <v>4029</v>
       </c>
       <c r="H212" s="2"/>
       <c r="I212" s="2"/>
@@ -19426,7 +19423,7 @@
         <v>19</v>
       </c>
       <c r="G213" s="2" t="s">
-        <v>4030</v>
+        <v>4029</v>
       </c>
       <c r="H213" s="2"/>
       <c r="I213" s="2"/>
@@ -19451,7 +19448,7 @@
         <v>19</v>
       </c>
       <c r="G214" s="2" t="s">
-        <v>4030</v>
+        <v>4029</v>
       </c>
       <c r="H214" s="2"/>
       <c r="I214" s="2"/>
@@ -19476,7 +19473,7 @@
         <v>19</v>
       </c>
       <c r="G215" s="2" t="s">
-        <v>4030</v>
+        <v>4029</v>
       </c>
       <c r="H215" s="6"/>
       <c r="I215" s="2"/>
@@ -19499,7 +19496,7 @@
       <c r="E216" s="190"/>
       <c r="F216" s="26"/>
       <c r="G216" s="126" t="s">
-        <v>4017</v>
+        <v>31</v>
       </c>
       <c r="H216" s="2"/>
       <c r="I216" s="2"/>
@@ -19525,7 +19522,7 @@
       <c r="E217" s="190"/>
       <c r="F217" s="26"/>
       <c r="G217" s="126" t="s">
-        <v>4017</v>
+        <v>31</v>
       </c>
       <c r="H217" s="2"/>
       <c r="I217" s="2"/>
@@ -19551,7 +19548,7 @@
       <c r="E218" s="190"/>
       <c r="F218" s="26"/>
       <c r="G218" s="126" t="s">
-        <v>4030</v>
+        <v>4029</v>
       </c>
       <c r="H218" s="2"/>
       <c r="I218" s="2"/>
@@ -19577,7 +19574,7 @@
       <c r="E219" s="190"/>
       <c r="F219" s="26"/>
       <c r="G219" s="126" t="s">
-        <v>4030</v>
+        <v>4029</v>
       </c>
       <c r="H219" s="2"/>
       <c r="I219" s="2"/>
@@ -19605,7 +19602,7 @@
         <v>19</v>
       </c>
       <c r="G220" s="126" t="s">
-        <v>4030</v>
+        <v>4029</v>
       </c>
       <c r="H220" s="2"/>
       <c r="I220" s="2"/>
@@ -19630,7 +19627,7 @@
         <v>19</v>
       </c>
       <c r="G221" s="126" t="s">
-        <v>4030</v>
+        <v>4029</v>
       </c>
       <c r="H221" s="2"/>
       <c r="I221" s="2"/>
@@ -19655,7 +19652,7 @@
         <v>19</v>
       </c>
       <c r="G222" s="126" t="s">
-        <v>4030</v>
+        <v>4029</v>
       </c>
       <c r="H222" s="2"/>
       <c r="I222" s="2"/>
@@ -19664,16 +19661,16 @@
     </row>
     <row r="223" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B223" s="25" t="s">
-        <v>4020</v>
+        <v>4019</v>
       </c>
       <c r="C223" s="26" t="s">
-        <v>4025</v>
+        <v>4024</v>
       </c>
       <c r="D223" s="116"/>
       <c r="E223" s="190"/>
       <c r="F223" s="33"/>
       <c r="G223" s="2" t="s">
-        <v>4017</v>
+        <v>31</v>
       </c>
       <c r="H223" s="2"/>
       <c r="I223" s="2"/>
@@ -19682,16 +19679,16 @@
     </row>
     <row r="224" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B224" s="25" t="s">
-        <v>4021</v>
+        <v>4020</v>
       </c>
       <c r="C224" s="26" t="s">
-        <v>4026</v>
+        <v>4025</v>
       </c>
       <c r="D224" s="116"/>
       <c r="E224" s="190"/>
       <c r="F224" s="33"/>
       <c r="G224" s="2" t="s">
-        <v>4017</v>
+        <v>31</v>
       </c>
       <c r="H224" s="2"/>
       <c r="I224" s="2"/>
@@ -19700,32 +19697,32 @@
     </row>
     <row r="225" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B225" s="25" t="s">
-        <v>4022</v>
+        <v>4021</v>
       </c>
       <c r="C225" s="26" t="s">
-        <v>4027</v>
+        <v>4026</v>
       </c>
       <c r="D225" s="116"/>
       <c r="E225" s="190"/>
       <c r="F225" s="33"/>
       <c r="G225" s="2" t="s">
-        <v>4017</v>
+        <v>31</v>
       </c>
       <c r="H225" s="2"/>
       <c r="K225" s="11"/>
     </row>
     <row r="226" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B226" s="25" t="s">
-        <v>4023</v>
+        <v>4022</v>
       </c>
       <c r="C226" s="26" t="s">
-        <v>4028</v>
+        <v>4027</v>
       </c>
       <c r="D226" s="116"/>
       <c r="E226" s="190"/>
       <c r="F226" s="33"/>
       <c r="G226" s="2" t="s">
-        <v>4017</v>
+        <v>31</v>
       </c>
       <c r="H226" s="2"/>
       <c r="K226" s="11"/>
@@ -19735,10 +19732,10 @@
         <v>220</v>
       </c>
       <c r="B227" s="25" t="s">
-        <v>4024</v>
+        <v>4023</v>
       </c>
       <c r="C227" s="26" t="s">
-        <v>4029</v>
+        <v>4028</v>
       </c>
       <c r="D227" s="116">
         <v>1053.4000000000001</v>
@@ -19748,7 +19745,7 @@
         <v>19</v>
       </c>
       <c r="G227" s="2" t="s">
-        <v>4017</v>
+        <v>31</v>
       </c>
       <c r="H227" s="2"/>
       <c r="K227" s="11"/>
@@ -19771,7 +19768,7 @@
         <v>19</v>
       </c>
       <c r="G228" s="2" t="s">
-        <v>4017</v>
+        <v>31</v>
       </c>
       <c r="H228" s="2"/>
       <c r="K228" s="11"/>
@@ -21437,7 +21434,7 @@
         <v>19</v>
       </c>
       <c r="G296" s="2" t="s">
-        <v>4031</v>
+        <v>3978</v>
       </c>
       <c r="H296" s="2"/>
       <c r="I296" s="2"/>
@@ -21462,7 +21459,7 @@
         <v>19</v>
       </c>
       <c r="G297" s="2" t="s">
-        <v>4031</v>
+        <v>3978</v>
       </c>
       <c r="H297" s="2"/>
       <c r="I297" s="2"/>
@@ -24184,7 +24181,7 @@
         <v>19</v>
       </c>
       <c r="G413" s="2" t="s">
-        <v>4017</v>
+        <v>31</v>
       </c>
       <c r="K413" s="11"/>
     </row>
@@ -24206,7 +24203,7 @@
         <v>19</v>
       </c>
       <c r="G414" s="2" t="s">
-        <v>4032</v>
+        <v>4031</v>
       </c>
       <c r="K414" s="11"/>
     </row>
@@ -24228,7 +24225,7 @@
         <v>19</v>
       </c>
       <c r="G415" s="2" t="s">
-        <v>4032</v>
+        <v>4031</v>
       </c>
       <c r="K415" s="11"/>
     </row>
@@ -24250,7 +24247,7 @@
         <v>19</v>
       </c>
       <c r="G416" s="2" t="s">
-        <v>4032</v>
+        <v>4031</v>
       </c>
       <c r="K416" s="11"/>
     </row>
@@ -24622,7 +24619,7 @@
         <v>19</v>
       </c>
       <c r="G433" s="2" t="s">
-        <v>4017</v>
+        <v>31</v>
       </c>
       <c r="K433" s="4"/>
     </row>
@@ -25456,21 +25453,21 @@
         <v>19</v>
       </c>
       <c r="G472" s="2" t="s">
-        <v>4017</v>
+        <v>31</v>
       </c>
     </row>
     <row r="473" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B473" s="25" t="s">
+        <v>4032</v>
+      </c>
+      <c r="C473" s="26" t="s">
         <v>4033</v>
-      </c>
-      <c r="C473" s="26" t="s">
-        <v>4034</v>
       </c>
       <c r="D473" s="117"/>
       <c r="E473" s="190"/>
       <c r="F473" s="33"/>
       <c r="G473" s="2" t="s">
-        <v>4017</v>
+        <v>31</v>
       </c>
     </row>
     <row r="474" spans="1:7" x14ac:dyDescent="0.25">
@@ -26331,7 +26328,7 @@
         <v>19</v>
       </c>
       <c r="G514" s="2" t="s">
-        <v>4032</v>
+        <v>4031</v>
       </c>
     </row>
     <row r="515" spans="1:7" x14ac:dyDescent="0.25">
@@ -26730,7 +26727,7 @@
         <v>19</v>
       </c>
       <c r="G533" s="2" t="s">
-        <v>4035</v>
+        <v>4034</v>
       </c>
     </row>
     <row r="534" spans="1:7" x14ac:dyDescent="0.25">
@@ -26961,7 +26958,7 @@
         <v>19</v>
       </c>
       <c r="G544" s="2" t="s">
-        <v>4036</v>
+        <v>4035</v>
       </c>
     </row>
     <row r="545" spans="1:7" x14ac:dyDescent="0.25">
@@ -27533,7 +27530,7 @@
     </row>
     <row r="572" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B572" s="25" t="s">
-        <v>4038</v>
+        <v>4037</v>
       </c>
       <c r="C572" s="26" t="s">
         <v>1491</v>
@@ -27547,7 +27544,7 @@
     </row>
     <row r="573" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B573" s="25" t="s">
-        <v>4037</v>
+        <v>4036</v>
       </c>
       <c r="C573" s="26" t="s">
         <v>1041</v>
@@ -27564,10 +27561,10 @@
         <v>565</v>
       </c>
       <c r="B574" s="25" t="s">
+        <v>4038</v>
+      </c>
+      <c r="C574" s="26" t="s">
         <v>4039</v>
-      </c>
-      <c r="C574" s="26" t="s">
-        <v>4040</v>
       </c>
       <c r="D574" s="116">
         <v>8119.7</v>
@@ -27598,7 +27595,7 @@
         <v>19</v>
       </c>
       <c r="G575" s="2" t="s">
-        <v>4031</v>
+        <v>4030</v>
       </c>
     </row>
     <row r="576" spans="1:7" x14ac:dyDescent="0.25">
@@ -27619,21 +27616,21 @@
         <v>19</v>
       </c>
       <c r="G576" s="2" t="s">
-        <v>4031</v>
+        <v>4030</v>
       </c>
     </row>
     <row r="577" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B577" s="25" t="s">
+        <v>4040</v>
+      </c>
+      <c r="C577" s="26" t="s">
         <v>4041</v>
-      </c>
-      <c r="C577" s="26" t="s">
-        <v>4042</v>
       </c>
       <c r="D577" s="116"/>
       <c r="E577" s="190"/>
       <c r="F577" s="33"/>
       <c r="G577" s="2" t="s">
-        <v>4031</v>
+        <v>4030</v>
       </c>
     </row>
     <row r="578" spans="1:7" x14ac:dyDescent="0.25">
@@ -28809,7 +28806,7 @@
         <v>19</v>
       </c>
       <c r="G633" s="2" t="s">
-        <v>4017</v>
+        <v>31</v>
       </c>
     </row>
     <row r="634" spans="1:7" x14ac:dyDescent="0.25">
@@ -29647,7 +29644,7 @@
         <v>19</v>
       </c>
       <c r="G673" s="2" t="s">
-        <v>4043</v>
+        <v>4042</v>
       </c>
     </row>
     <row r="674" spans="1:7" x14ac:dyDescent="0.25">
@@ -29668,7 +29665,7 @@
         <v>19</v>
       </c>
       <c r="G674" s="2" t="s">
-        <v>4043</v>
+        <v>4042</v>
       </c>
     </row>
     <row r="675" spans="1:7" x14ac:dyDescent="0.25">
